--- a/References/C_Input/Final_C_input_Calculation.xlsx
+++ b/References/C_Input/Final_C_input_Calculation.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mihirbendre/Documents/Gazelle/Gazelle_2025/Ghana_Project/SOC Modeling/RothC/RothC_Implementation/Documentation/axam-docs/References/C_Input/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mihirbendre/Documents/Gazelle/Gazelle_2025/Ghana_Project/QA1_&amp;_3/Documentation/axam-docs/References/C_Input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC2A099E-B793-494E-8EEC-A03A6E01AF3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4086E3EC-D890-9947-942D-5FE20C391585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="8320" windowWidth="28040" windowHeight="10040" xr2:uid="{3B82E5F8-9135-5B44-BE62-EE1F71B6AA73}"/>
+    <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" xr2:uid="{3B82E5F8-9135-5B44-BE62-EE1F71B6AA73}"/>
   </bookViews>
   <sheets>
-    <sheet name="Final_C_input_Calculation" sheetId="1" r:id="rId1"/>
+    <sheet name="C_input_Calculation_new" sheetId="3" r:id="rId1"/>
+    <sheet name="Aside" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="54">
   <si>
     <t>region</t>
   </si>
@@ -41,9 +42,6 @@
     <t>crop</t>
   </si>
   <si>
-    <t>yield</t>
-  </si>
-  <si>
     <t>sem</t>
   </si>
   <si>
@@ -56,9 +54,6 @@
     <t>rs_ratio</t>
   </si>
   <si>
-    <t>carbon_input</t>
-  </si>
-  <si>
     <t>UPPER WEST</t>
   </si>
   <si>
@@ -170,9 +165,6 @@
     <t>Annual C-input to soil</t>
   </si>
   <si>
-    <t>baseline</t>
-  </si>
-  <si>
     <t>Project</t>
   </si>
   <si>
@@ -183,6 +175,27 @@
   </si>
   <si>
     <t>C-input base</t>
+  </si>
+  <si>
+    <t>yield (t/ha)</t>
+  </si>
+  <si>
+    <t>yield (kg/acre)</t>
+  </si>
+  <si>
+    <t>yield (MT/ha)</t>
+  </si>
+  <si>
+    <t>typical</t>
+  </si>
+  <si>
+    <t>yield (tons/ha)</t>
+  </si>
+  <si>
+    <t>project_c_inp</t>
+  </si>
+  <si>
+    <t>baseline_c_inp</t>
   </si>
 </sst>
 </file>
@@ -338,7 +351,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -516,6 +529,18 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -679,12 +704,14 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1059,7 +1086,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CB8F999-A1C5-D445-9BD8-A8946719E5FB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81F32D67-920B-1845-8257-A3B45A991681}">
   <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1076,33 +1103,33 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
+      <c r="H1" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C2">
         <v>1.4279885059999999</v>
@@ -1119,19 +1146,19 @@
       <c r="G2">
         <v>0.1</v>
       </c>
-      <c r="H2">
-        <v>0.35560113999999998</v>
-      </c>
-      <c r="I2" s="2">
-        <v>0.10142064675861499</v>
+      <c r="H2" s="2">
+        <v>0.90752427000000002</v>
+      </c>
+      <c r="I2">
+        <v>0.76829539499999999</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
         <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
       </c>
       <c r="C3">
         <v>1.4554225350000001</v>
@@ -1148,19 +1175,19 @@
       <c r="G3">
         <v>0.2</v>
       </c>
-      <c r="H3">
-        <v>0.60749336099999995</v>
-      </c>
-      <c r="I3" s="2">
-        <v>0.195344542880168</v>
+      <c r="H3" s="2">
+        <v>4.2114881500000001</v>
+      </c>
+      <c r="I3">
+        <v>3.5719583660000001</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C4">
         <v>14.63344828</v>
@@ -1177,19 +1204,19 @@
       <c r="G4">
         <v>1</v>
       </c>
-      <c r="H4">
-        <v>1.1097562379999999</v>
-      </c>
-      <c r="I4" s="2">
-        <v>0.247172980316304</v>
+      <c r="H4" s="2">
+        <v>21.141481899999999</v>
+      </c>
+      <c r="I4">
+        <v>19.824471509999999</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C5">
         <v>1.0256647400000001</v>
@@ -1206,19 +1233,19 @@
       <c r="G5">
         <v>0.01</v>
       </c>
-      <c r="H5">
-        <v>0.317913426</v>
-      </c>
-      <c r="I5" s="2">
-        <v>6.6330390000000003E-2</v>
+      <c r="H5" s="2">
+        <v>1.23051847</v>
+      </c>
+      <c r="I5">
+        <v>1.0045185489999999</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C6">
         <v>0.89034682099999995</v>
@@ -1235,19 +1262,19 @@
       <c r="G6">
         <v>0.2</v>
       </c>
-      <c r="H6">
-        <v>0.30403671100000002</v>
-      </c>
-      <c r="I6" s="2">
-        <v>0.10027434050828</v>
+      <c r="H6" s="2">
+        <v>1.08784945</v>
+      </c>
+      <c r="I6">
+        <v>0.93230062499999999</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C7">
         <v>1.3395348840000001</v>
@@ -1264,19 +1291,19 @@
       <c r="G7">
         <v>0.1</v>
       </c>
-      <c r="H7">
-        <v>0.4149949</v>
-      </c>
-      <c r="I7" s="2">
-        <v>0.114137561072662</v>
+      <c r="H7" s="2">
+        <v>1.2836097799999999</v>
+      </c>
+      <c r="I7">
+        <v>1.078335109</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C8">
         <v>0.90666666699999998</v>
@@ -1293,19 +1320,19 @@
       <c r="G8">
         <v>0.1</v>
       </c>
-      <c r="H8">
-        <v>0.33527831200000002</v>
-      </c>
-      <c r="I8" s="2">
-        <v>8.9201970000000005E-2</v>
+      <c r="H8" s="2">
+        <v>1.6460045800000001</v>
+      </c>
+      <c r="I8">
+        <v>1.372821968</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C9">
         <v>1.0646956519999999</v>
@@ -1322,30 +1349,30 @@
       <c r="G9">
         <v>0.09</v>
       </c>
-      <c r="H9">
-        <v>0.32618866299999999</v>
-      </c>
-      <c r="I9" s="2">
-        <v>8.6952550000000003E-2</v>
+      <c r="H9" s="2">
+        <v>1.13770806</v>
+      </c>
+      <c r="I9">
+        <v>0.95169946999999999</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B13" s="4">
         <v>0.6</v>
@@ -1354,7 +1381,7 @@
         <v>0.6</v>
       </c>
       <c r="E13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -1365,7 +1392,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B14" s="1">
         <v>0.7</v>
@@ -1374,7 +1401,7 @@
         <v>0.7</v>
       </c>
       <c r="E14" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1385,7 +1412,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B15" s="1">
         <v>0.15</v>
@@ -1394,7 +1421,7 @@
         <v>0.15</v>
       </c>
       <c r="E15" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1405,7 +1432,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1">
         <v>0.05</v>
@@ -1414,7 +1441,7 @@
         <v>0.05</v>
       </c>
       <c r="E16" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1425,7 +1452,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B17" s="1">
         <v>0.15</v>
@@ -1434,7 +1461,7 @@
         <v>0.15</v>
       </c>
       <c r="E17" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1445,7 +1472,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="E18" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1456,7 +1483,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B19" s="4">
         <v>0.3</v>
@@ -1465,7 +1492,7 @@
         <v>0.3</v>
       </c>
       <c r="E19" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1476,7 +1503,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B20" s="1">
         <v>0.5</v>
@@ -1485,7 +1512,7 @@
         <v>0.5</v>
       </c>
       <c r="E20" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1496,7 +1523,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B21" s="1">
         <v>0.2</v>
@@ -1505,7 +1532,7 @@
         <v>0.2</v>
       </c>
       <c r="E21" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1516,7 +1543,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B22" s="1">
         <v>0.25</v>
@@ -1525,20 +1552,20 @@
         <v>0.25</v>
       </c>
       <c r="E22" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F22">
         <f>B31</f>
-        <v>0.46445872815</v>
+        <v>3.4114199298999992</v>
       </c>
       <c r="G22">
         <f>C31</f>
-        <v>0.12417142570561152</v>
+        <v>3.0747556947299999</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B23" s="1">
         <v>0.05</v>
@@ -1547,7 +1574,7 @@
         <v>0.05</v>
       </c>
       <c r="E23" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -1558,7 +1585,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="E24" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1569,7 +1596,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B25" s="4">
         <v>0.1</v>
@@ -1580,7 +1607,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B26" s="1">
         <v>0.7</v>
@@ -1591,7 +1618,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B27" s="1">
         <v>0.3</v>
@@ -1602,26 +1629,246 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B30" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B31">
         <f>(H2*B14+H3*B17+H5*B15+H6*B16)*B13+(H4*B26+H4*B27)*B25+(B20*H7+B21*H8+B22*H9+B23*H9)*B19</f>
-        <v>0.46445872815</v>
+        <v>3.4114199298999992</v>
       </c>
       <c r="C31">
         <f>(I2*C14+I3*C17+I5*C15+I6*C16)*C13+(I4*C26+I4*C27)*C25+(C20*I7+C21*I8+C22*I9+C23*I9)*C19</f>
-        <v>0.12417142570561152</v>
+        <v>3.0747556947299999</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B30FE20-7BE1-7749-B95B-2B75F672AEC0}">
+  <dimension ref="B2:D22"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="13.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>1.4279885059999999</v>
+      </c>
+      <c r="D3">
+        <f>C3*404.686</f>
+        <v>577.886956539116</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>1.4554225350000001</v>
+      </c>
+      <c r="D4">
+        <f t="shared" ref="D4:D10" si="0">C4*404.686</f>
+        <v>588.98912399900996</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5">
+        <v>14.63344828</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="0"/>
+        <v>5921.9516506400796</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>1.0256647400000001</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="0"/>
+        <v>415.07216097164002</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7">
+        <v>0.89034682099999995</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>360.31089360320595</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8">
+        <v>1.3395348840000001</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="0"/>
+        <v>542.09101406642401</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9">
+        <v>0.90666666699999998</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="0"/>
+        <v>366.915306801562</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10">
+        <v>1.0646956519999999</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="0"/>
+        <v>430.86742462527195</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="6">
+        <v>1.4279885059999999</v>
+      </c>
+      <c r="D15" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>1.4554225350000001</v>
+      </c>
+      <c r="D16" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17">
+        <v>14.63344828</v>
+      </c>
+      <c r="D17">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="5">
+        <v>1.0256647400000001</v>
+      </c>
+      <c r="D18" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19">
+        <v>0.89034682099999995</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20">
+        <v>1.3395348840000001</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21">
+        <v>0.90666666699999998</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B22" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22">
+        <v>1.0646956519999999</v>
+      </c>
+      <c r="D22">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>